--- a/documents/shenzhen_air/航空货物明细表.xlsx
+++ b/documents/shenzhen_air/航空货物明细表.xlsx
@@ -2,15 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="HighLightColumn">0</definedName>
+    <definedName name="HighLightRow">0</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -49,7 +51,7 @@
     <t>件数：</t>
   </si>
   <si>
-    <t>18件296KG 2025年12月11日</t>
+    <t>18件296KG</t>
   </si>
   <si>
     <t>货物名称</t>
@@ -126,34 +128,34 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Arial Unicode MS"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial Unicode MS"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -504,42 +506,42 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -646,180 +648,189 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -884,9 +895,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -900,31 +911,31 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
@@ -996,40 +1007,66 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1043,38 +1080,20 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
@@ -1132,11 +1151,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="9.65740740740741" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="7" max="7" width="16.3796296296296" customWidth="1"/>
+    <col min="9" max="9" width="7.51851851851852" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="20.4" customHeight="1" spans="1:9">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1149,348 +1174,350 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" ht="31.2" customHeight="1" spans="1:9">
-      <c r="A3" s="2" t="s">
+    <row r="2" ht="32.25" customHeight="1" spans="1:9">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" ht="27.75" customHeight="1" spans="1:9">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:9">
-      <c r="A4" s="6" t="s">
+      <c r="H3" s="8">
+        <v>45909</v>
+      </c>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" ht="26.25" customHeight="1" spans="1:9">
+      <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="7" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:9">
-      <c r="A5" s="8" t="s">
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="8" t="s">
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:9">
-      <c r="A7" s="8" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:9">
-      <c r="A8" s="8" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:9">
-      <c r="A9" s="8" t="s">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:9">
-      <c r="A10" s="8" t="s">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+    </row>
+    <row r="10" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:9">
-      <c r="A11" s="8" t="s">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+    </row>
+    <row r="11" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A11" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:9">
-      <c r="A12" s="8" t="s">
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:9">
-      <c r="A13" s="8" t="s">
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:9">
-      <c r="A14" s="8" t="s">
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A14" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:9">
-      <c r="A15" s="8" t="s">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A15" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:9">
-      <c r="A16" s="8" t="s">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+    </row>
+    <row r="16" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" customHeight="1" spans="1:9">
-      <c r="A17" s="8" t="s">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+    </row>
+    <row r="17" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A17" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:9">
-      <c r="A18" s="8" t="s">
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+    </row>
+    <row r="18" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A18" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="19" customHeight="1" spans="1:9">
-      <c r="A19" s="8" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+    </row>
+    <row r="19" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A19" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-    </row>
-    <row r="20" customHeight="1" spans="1:9">
-      <c r="A20" s="8" t="s">
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+    </row>
+    <row r="20" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A20" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-    </row>
-    <row r="21" customHeight="1" spans="1:9">
-      <c r="A21" s="8" t="s">
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+    </row>
+    <row r="21" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:9">
-      <c r="A22" s="8" t="s">
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+    </row>
+    <row r="22" ht="25.5" customHeight="1" spans="1:9">
+      <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-    </row>
-    <row r="23" customHeight="1" spans="1:9">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="12"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="H3:I3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A6:G6"/>
@@ -1510,36 +1537,12 @@
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G27"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="H4:I27"/>
-    <mergeCell ref="A23:G27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/documents/shenzhen_air/航空货物明细表.xlsx
+++ b/documents/shenzhen_air/航空货物明细表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
@@ -118,11 +118,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -818,7 +819,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="31" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1208,7 +1209,7 @@
       <c r="H3" s="8">
         <v>45909</v>
       </c>
-      <c r="I3" s="7"/>
+      <c r="I3" s="8"/>
     </row>
     <row r="4" ht="26.25" customHeight="1" spans="1:9">
       <c r="A4" s="9" t="s">

--- a/documents/shenzhen_air/航空货物明细表.xlsx
+++ b/documents/shenzhen_air/航空货物明细表.xlsx
@@ -135,19 +135,16 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
     </font>
@@ -794,7 +791,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -807,31 +804,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1200,19 +1200,19 @@
         <v>4</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="7">
         <v>45909</v>
       </c>
-      <c r="I3" s="8"/>
+      <c r="I3" s="7"/>
     </row>
     <row r="4" ht="26.25" customHeight="1" spans="1:9">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="9"/>
@@ -1230,12 +1230,12 @@
       <c r="A5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
     </row>
@@ -1243,12 +1243,12 @@
       <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
     </row>
@@ -1256,12 +1256,12 @@
       <c r="A7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
@@ -1269,12 +1269,12 @@
       <c r="A8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
     </row>
@@ -1282,12 +1282,12 @@
       <c r="A9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
     </row>
@@ -1295,12 +1295,12 @@
       <c r="A10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
     </row>
@@ -1308,12 +1308,12 @@
       <c r="A11" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
     </row>
@@ -1321,12 +1321,12 @@
       <c r="A12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
     </row>
@@ -1334,12 +1334,12 @@
       <c r="A13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
     </row>
@@ -1347,12 +1347,12 @@
       <c r="A14" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
     </row>
@@ -1360,12 +1360,12 @@
       <c r="A15" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
     </row>
@@ -1373,12 +1373,12 @@
       <c r="A16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
     </row>
@@ -1386,12 +1386,12 @@
       <c r="A17" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
     </row>
@@ -1399,12 +1399,12 @@
       <c r="A18" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
     </row>
@@ -1412,12 +1412,12 @@
       <c r="A19" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
     </row>
@@ -1425,12 +1425,12 @@
       <c r="A20" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
     </row>
@@ -1438,12 +1438,12 @@
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
     </row>
@@ -1451,67 +1451,67 @@
       <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="12"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
     </row>
